--- a/resources/templates/reuse-analysis-template.xlsx
+++ b/resources/templates/reuse-analysis-template.xlsx
@@ -1,19 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssamba\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F633A9E-9892-4D48-ADEF-DF8C57B9521C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reuse Analysis" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reuse Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Fill">#REF!</definedName>
@@ -77,124 +70,36 @@
     <definedName name="YesNo">#REF!</definedName>
     <definedName name="yiyiu">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>Disciplines</t>
-  </si>
-  <si>
-    <t>Asset Family</t>
-  </si>
-  <si>
-    <t>Asset Model</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Required Qty</t>
-  </si>
-  <si>
-    <t>Total Need Cost</t>
-  </si>
-  <si>
-    <t>Transfer Cost</t>
-  </si>
-  <si>
-    <t>Reuse Qty</t>
-  </si>
-  <si>
-    <t>Reuse Value</t>
-  </si>
-  <si>
-    <t>Net Saving</t>
-  </si>
-  <si>
-    <t>To Buy</t>
-  </si>
-  <si>
-    <t>Amount to Buy</t>
-  </si>
-  <si>
-    <t>Reused Asset List (S/N)</t>
-  </si>
-  <si>
-    <t>MECHANICAL</t>
-  </si>
-  <si>
-    <t>Measuring Instruments</t>
-  </si>
-  <si>
-    <t>RT-ZC02</t>
-  </si>
-  <si>
-    <t>LABORATORY</t>
-  </si>
-  <si>
-    <t>Measurement, Visualization and Analysis</t>
-  </si>
-  <si>
-    <t>Logic 8</t>
-  </si>
-  <si>
-    <t>SYSTEMS</t>
-  </si>
-  <si>
-    <t>Controllers</t>
-  </si>
-  <si>
-    <t>PXIe-8364</t>
-  </si>
-  <si>
-    <t>HARDWARE</t>
-  </si>
-  <si>
-    <t>Electronic Loads</t>
-  </si>
-  <si>
-    <t>EL 9080-60 DT</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Multiplexer - 40-632A-021-48/1</t>
-  </si>
-  <si>
-    <t>Total (USD)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -312,89 +217,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -718,314 +682,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:T9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="0.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
-    <col min="9" max="9" width="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="1.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="1.28515625" customWidth="1"/>
-    <col min="20" max="20" width="38.42578125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" customWidth="1"/>
+    <col width="3.28515625" customWidth="1" min="1" max="1"/>
+    <col width="16.85546875" customWidth="1" min="2" max="2"/>
+    <col width="39.28515625" customWidth="1" min="3" max="3"/>
+    <col width="26.42578125" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" style="1" min="5" max="5"/>
+    <col width="0.7109375" customWidth="1" min="6" max="6"/>
+    <col width="13.42578125" customWidth="1" min="7" max="7"/>
+    <col width="18.42578125" customWidth="1" min="8" max="8"/>
+    <col width="1" customWidth="1" min="9" max="9"/>
+    <col width="14.85546875" customWidth="1" min="10" max="10"/>
+    <col width="1" customWidth="1" min="11" max="11"/>
+    <col width="11.5703125" customWidth="1" style="2" min="12" max="12"/>
+    <col width="12.140625" customWidth="1" style="2" min="13" max="13"/>
+    <col width="1.140625" customWidth="1" style="2" min="14" max="14"/>
+    <col width="13.5703125" customWidth="1" min="15" max="15"/>
+    <col width="1.5703125" customWidth="1" min="16" max="16"/>
+    <col width="10.42578125" customWidth="1" style="2" min="17" max="17"/>
+    <col width="14.42578125" customWidth="1" style="2" min="18" max="18"/>
+    <col width="1.28515625" customWidth="1" min="19" max="19"/>
+    <col width="38.42578125" customWidth="1" style="3" min="20" max="20"/>
+    <col width="12.42578125" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+    <row r="1"/>
+    <row r="2" ht="15" customHeight="1" thickBot="1">
+      <c r="K2" s="2" t="n"/>
     </row>
-    <row r="3" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="3" ht="15" customHeight="1" thickBot="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Reference Price</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Total Need Cost</t>
+        </is>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>Transfer Cost</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Reuse Qty</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Reuse Value</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>Net Saving</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Shortfall</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>Amount to Buy</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Reused Asset List (S/N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>MECHANICAL</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Measuring Instruments</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>RT-ZC02</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="N4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>LABORATORY</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Measurement, Visualization and Analysis</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Logic 8</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Controllers</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>PXIe-8364</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="J6" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>HARDWARE</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Electronic Loads</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>EL 9080-60 DT</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>HARDWARE</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Multiplexer - 40-632A-021-48/1</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="G8" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n"/>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="13">
-        <v>150</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="12">
-        <v>3</v>
-      </c>
-      <c r="H4" s="13">
-        <v>450</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="13">
-        <v>0</v>
-      </c>
-      <c r="O4" s="28">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="13">
-        <v>3</v>
-      </c>
-      <c r="R4" s="13">
-        <v>450</v>
-      </c>
-      <c r="T4" s="14"/>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="12">
-        <v>150</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12">
-        <v>3</v>
-      </c>
-      <c r="H5" s="12">
-        <v>450</v>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12">
-        <v>0</v>
-      </c>
-      <c r="M5" s="12">
-        <v>450</v>
-      </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12">
-        <v>450</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>0</v>
-      </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="12">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12">
-        <v>4</v>
-      </c>
-      <c r="H6" s="12">
-        <v>6000</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12">
-        <v>6000</v>
-      </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12">
-        <v>6000</v>
-      </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12">
-        <v>0</v>
-      </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="12">
-        <v>800</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12">
-        <v>6</v>
-      </c>
-      <c r="H7" s="12">
-        <v>4800</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12">
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <v>4800</v>
-      </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12">
-        <v>4800</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
-        <v>0</v>
-      </c>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="12">
-        <v>1500</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12">
-        <v>4</v>
-      </c>
-      <c r="H8" s="12">
-        <v>6000</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>6000</v>
-      </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12">
-        <v>6000</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
-        <v>0</v>
-      </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-    </row>
-    <row r="9" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="19">
+    <row r="9" ht="15" customHeight="1" thickBot="1">
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Total (USD)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="19" t="n">
         <v>17700</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="19">
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="19" t="n">
         <v>17250</v>
       </c>
-      <c r="O9" s="23">
+      <c r="K9" s="23" t="n">
         <v>17250</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="19">
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="19" t="n">
         <v>450</v>
       </c>
     </row>
